--- a/Unit_Test_Plan_v0_1.xlsx
+++ b/Unit_Test_Plan_v0_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,126 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TC-27: Java Try-with-Resources Nesting Complexity</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Submit Java code utilizing try-with-resources with an inner while loop</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Nesting counter ignores resource declarations; nesting depth calculated as 1 or 2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0 Excessive Nesting findings reported; 100/100 Health Score if no other bugs</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TC-28: Scan History Details API (/scan/{id})</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Send GET request to /api/v1/submit/scan/{scan_id}</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Full raw_code, all findings, executive summary, and severity counts returned</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HTTP 200 with complete scan details, raw code, and all findings</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TC-29: Scan History Cascade Deletion (DELETE /{id})</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Send DELETE request to /api/v1/submit/{scan_id}</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Scan and all child records (findings, chat messages, fix records) are removed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HTTP 200 with {"status": "deleted", "scan_id": scan_id}</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TC-30: History Search &amp; Multi-Filter Querying</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Execute search query and filter by Java and Clean status in History UI</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>History card list reacts in real time and shows filtered subset accurately</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Instant UI update displaying only matching scans</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
